--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260618.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260618.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>42,460,027</t>
+          <t>42,152,027</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>63.86%</t>
+          <t>63.30%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2,558,703</t>
+          <t>2,545,703</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.20%</t>
+          <t>6.96%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>21,230,000</t>
+          <t>21,112,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.64%</t>
+          <t>3.53%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>5,710,267</t>
+          <t>5,736,267</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>20,288,286</t>
+          <t>20,168,286</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>498,000</t>
+          <t>503,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2,321,901</t>
+          <t>2,280,901</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>4,593,285</t>
+          <t>4,570,285</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>564,222</t>
+          <t>553,222</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -831,73 +831,73 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>5,431,296</t>
+          <t>5,348,296</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>202607WTEN6F</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>電子指數期貨</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>1,188,617</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>180,515</t>
+          <t>1,166,617</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>202607WTEN6F</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>電子指數期貨</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>179,515</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,83 +909,83 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>5,324,520</t>
+          <t>1,972,288</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>167,000</t>
+          <t>1,318,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>1,955,288</t>
+          <t>5,220,520</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>599,600</t>
+          <t>162,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,272,000</t>
+          <t>12,691,134</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,127 +1019,127 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>12,804,134</t>
+          <t>594,600</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>144,482</t>
+          <t>3,382,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>99,000</t>
+          <t>844,349</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>3,381,000</t>
+          <t>99,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>310,672</t>
+          <t>138,482</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>846,349</t>
+          <t>308,672</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,39 +1151,39 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>137,921</t>
+          <t>150,499</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>146,499</t>
+          <t>135,921</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1205,29 +1205,29 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>1,893,321</t>
+          <t>1,880,321</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>1,001,822</t>
+          <t>3,176,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,22 +1239,22 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>3,066,000</t>
+          <t>987,822</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,726,000</t>
+          <t>1,806,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,61 +1283,61 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>778,000</t>
+          <t>1,179,441</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,202,441</t>
+          <t>758,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>5,638,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>5,610,000</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>563,000</t>
+          <t>569,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>798,897</t>
+          <t>796,897</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,535,384</t>
+          <t>574,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>938,659</t>
+          <t>923,659</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
@@ -1469,56 +1469,56 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>145,386</t>
+          <t>143,386</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>577,000</t>
+          <t>370,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>371,000</t>
+          <t>1,359,384</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>4,475,578</t>
+          <t>4,389,578</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>3,351,981</t>
+          <t>3,429,981</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>2,575,703</t>
+          <t>2,559,703</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
@@ -1601,29 +1601,29 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>10,381,121</t>
+          <t>10,447,121</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>7,349,249</t>
+          <t>490,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,22 +1635,22 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>202607WVHFN6F</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>7,065,249</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.17%</t>
         </is>
       </c>
     </row>
@@ -1667,51 +1667,51 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>2,132,107</t>
+          <t>2,159,107</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>202607WVHFN6F</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>5,015,956</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>828,000</t>
+          <t>179,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,22 +1723,22 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>179,000</t>
+          <t>92,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>113,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>90,000</t>
+          <t>4,888,956</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>1,187,076</t>
+          <t>793,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,22 +1811,22 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>294,000</t>
+          <t>1,168,076</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>1,543,400</t>
+          <t>1,537,400</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,88 +1855,88 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>1,008,121</t>
+          <t>286,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>327,000</t>
+          <t>315,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>1,723,000</t>
+          <t>384,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>988,121</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
@@ -1953,156 +1953,306 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>176,000</t>
+          <t>175,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>787,000</t>
+          <t>168,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>692,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>486,000</t>
+          <t>154,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>63,000</t>
+          <t>326,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>347,702,308</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr"/>
+          <t>1,732,000</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>0.06%</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>424,905,235</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="inlineStr"/>
+          <t>250,000</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
+          <t>4919</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>新唐</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>331,000</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>3005</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>神基</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>670,000</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>113,000</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>0.03%</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>6526</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>達發</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>70,000</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>0.03%</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>347,772,202</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>M_NTD</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>MARGIN</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>437,295,365</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
           <t>PFUR_NTD</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>PAYABLES FOR UNITS REDEEMED</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>30,982,822</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr"/>
+      <c r="D95" s="4" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>RDI_NTD</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>245,374,593</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
